--- a/ci-cd-merge-resolver/repoCollector/datasets/unirest-java.xlsx
+++ b/ci-cd-merge-resolver/repoCollector/datasets/unirest-java.xlsx
@@ -141,7 +141,7 @@
         <v>12</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>274.0</v>
+        <v>384.0</v>
       </c>
       <c r="E2" t="n" s="0">
         <v>109.0</v>
@@ -156,10 +156,10 @@
         <v>1</v>
       </c>
       <c r="I2" t="n" s="0">
-        <v>2.1010000705718994</v>
+        <v>1.066999912261963</v>
       </c>
       <c r="J2" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
